--- a/backend/app/aud/obligaciones_fiscales/templates/dm_obligaciones_fiscales.xlsx
+++ b/backend/app/aud/obligaciones_fiscales/templates/dm_obligaciones_fiscales.xlsx
@@ -3946,11 +3946,7 @@
         </is>
       </c>
       <c r="D24" s="193" t="n"/>
-      <c r="E24" s="388" t="inlineStr">
-        <is>
-          <t>JAUS</t>
-        </is>
-      </c>
+      <c r="E24" s="388" t="n"/>
       <c r="F24" s="63" t="n"/>
       <c r="G24" s="145" t="n"/>
     </row>
@@ -4752,6 +4748,8 @@
       </c>
       <c r="G28" s="332" t="n"/>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="326" t="inlineStr">
         <is>
@@ -8980,6 +8978,7 @@
       <c r="D9" s="162" t="n"/>
       <c r="E9" s="196" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="207" t="n"/>
       <c r="B11" s="208" t="n"/>
@@ -10059,6 +10058,7 @@
       <c r="L41" s="79" t="n"/>
       <c r="M41" s="80" t="n"/>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="8" t="n"/>
     </row>
@@ -10508,6 +10508,8 @@
       <c r="E41" s="217" t="n"/>
     </row>
     <row r="42" ht="13.5" customHeight="1" thickTop="1"/>
+    <row r="43"/>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="170" t="inlineStr">
         <is>
@@ -10970,6 +10972,7 @@
       </c>
     </row>
     <row r="96" hidden="1" ht="13.5" customHeight="1" thickTop="1"/>
+    <row r="97"/>
     <row r="98">
       <c r="A98" s="8" t="n"/>
     </row>
@@ -12099,6 +12102,7 @@
       <c r="L35" s="31" t="n"/>
       <c r="M35" s="31" t="n"/>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="539" t="inlineStr">
         <is>
@@ -15124,6 +15128,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="B43" s="8" t="inlineStr">
         <is>
@@ -15213,6 +15218,7 @@
         <v/>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="463" t="inlineStr">
         <is>
@@ -15676,6 +15682,7 @@
         <v/>
       </c>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="C58" s="2" t="n"/>
     </row>
@@ -34516,6 +34523,7 @@
       <c r="D10" s="541" t="n"/>
       <c r="E10" s="541" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -34542,6 +34550,7 @@
       <c r="C14" s="275" t="n"/>
       <c r="D14" s="275" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
@@ -37110,17 +37119,16 @@
       <c r="A71" s="194" t="n"/>
       <c r="B71" s="8" t="n"/>
     </row>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
     <row r="75">
       <c r="A75" s="131" t="inlineStr">
         <is>
           <t>Elaborado por:</t>
         </is>
       </c>
-      <c r="B75" s="387" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
+      <c r="B75" s="387" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="131" t="inlineStr">
@@ -37128,11 +37136,7 @@
           <t>Revisado por:</t>
         </is>
       </c>
-      <c r="B76" s="387" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
+      <c r="B76" s="387" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="131" t="inlineStr">
@@ -40448,6 +40452,7 @@
         </is>
       </c>
     </row>
+    <row r="75"/>
     <row r="76" hidden="1">
       <c r="A76" s="233" t="inlineStr">
         <is>
@@ -40785,6 +40790,7 @@
       <c r="C84" s="217" t="n"/>
       <c r="H84" s="217" t="n"/>
     </row>
+    <row r="85"/>
     <row r="86">
       <c r="B86" s="32" t="inlineStr">
         <is>
@@ -41092,6 +41098,10 @@
         </is>
       </c>
     </row>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
+    <row r="107"/>
     <row r="108">
       <c r="B108" s="3" t="inlineStr">
         <is>

--- a/backend/app/aud/obligaciones_fiscales/templates/dm_obligaciones_fiscales.xlsx
+++ b/backend/app/aud/obligaciones_fiscales/templates/dm_obligaciones_fiscales.xlsx
@@ -9084,7 +9084,7 @@
         </is>
       </c>
       <c r="C14" s="117" t="n">
-        <v>1.210719302591201e-10</v>
+        <v>0</v>
       </c>
       <c r="D14" s="536">
         <f>+F14-C14</f>
@@ -9095,7 +9095,7 @@
         <v/>
       </c>
       <c r="F14" s="117" t="n">
-        <v>1.210719302591201e-10</v>
+        <v>0</v>
       </c>
       <c r="G14" s="120" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="C15" s="117" t="n">
-        <v>-3.979039320256561e-13</v>
+        <v>0</v>
       </c>
       <c r="D15" s="536">
         <f>+F15-C15</f>
@@ -9151,7 +9151,7 @@
         <v/>
       </c>
       <c r="F15" s="117" t="n">
-        <v>-3.979039320256561e-13</v>
+        <v>0</v>
       </c>
       <c r="G15" s="120" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="C17" s="117" t="n">
-        <v>3.319653579803017e-13</v>
+        <v>0</v>
       </c>
       <c r="D17" s="536">
         <f>+F17-C17</f>
@@ -9263,7 +9263,7 @@
         <v/>
       </c>
       <c r="F17" s="117" t="n">
-        <v>3.319653579803017e-13</v>
+        <v>0</v>
       </c>
       <c r="G17" s="120" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="C19" s="117" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>0</v>
       </c>
       <c r="D19" s="536">
         <f>+F19-C19</f>
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="C22" s="117" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>0</v>
       </c>
       <c r="D22" s="536">
         <f>+F22-C22</f>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="C23" s="117" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>0</v>
       </c>
       <c r="D23" s="536">
         <f>+F23-C23</f>
@@ -11431,16 +11431,12 @@
       <c r="C18" s="225" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="225" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="D18" s="225" t="n"/>
       <c r="E18" s="225" t="n"/>
       <c r="F18" s="225" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="225" t="n">
-        <v>0.5900000000000001</v>
-      </c>
+      <c r="G18" s="225" t="n"/>
       <c r="H18" s="225" t="n">
         <v>0</v>
       </c>
@@ -11883,16 +11879,12 @@
       <c r="C29" s="225" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="225" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="D29" s="225" t="n"/>
       <c r="E29" s="225" t="n"/>
       <c r="F29" s="225" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="225" t="n">
-        <v>0.59</v>
-      </c>
+      <c r="G29" s="225" t="n"/>
       <c r="H29" s="225" t="n">
         <v>0</v>
       </c>
@@ -14056,7 +14048,7 @@
       <c r="C15" s="225" t="n"/>
       <c r="D15" s="225" t="n"/>
       <c r="E15" s="225">
-        <f>620863.38-50</f>
+        <f>0-50</f>
         <v/>
       </c>
       <c r="F15" s="225" t="n"/>
@@ -18119,7 +18111,7 @@
         <v/>
       </c>
       <c r="Z22" s="257">
-        <f>4539.94+1641.2</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="AA22" s="256" t="n">
@@ -18586,7 +18578,7 @@
         <v/>
       </c>
       <c r="Z26" s="257">
-        <f>13141.75+2420.8</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="AA26" s="257" t="n">
@@ -18705,7 +18697,7 @@
         <v/>
       </c>
       <c r="Z27" s="257">
-        <f>11968.49+5154.81</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="AA27" s="257" t="n">
@@ -18940,7 +18932,7 @@
         <v/>
       </c>
       <c r="Z29" s="257">
-        <f>64304.92+3539.19</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="AA29" s="257" t="n">
@@ -19059,7 +19051,7 @@
         <v/>
       </c>
       <c r="Z30" s="257">
-        <f>76906.31+6753.43</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="AA30" s="257" t="n">
@@ -35926,9 +35918,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="15" t="n"/>
-      <c r="U41" s="15" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="U41" s="15" t="n"/>
       <c r="V41" s="283">
         <f>SUM(J41:U41)</f>
         <v/>
@@ -36332,32 +36322,16 @@
       <c r="G46" s="281" t="n"/>
       <c r="H46" s="281" t="n"/>
       <c r="I46" s="281" t="n"/>
-      <c r="J46" s="15" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K46" s="15" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="L46" s="15" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="M46" s="15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="N46" s="15" t="n">
-        <v>0.57</v>
-      </c>
+      <c r="J46" s="15" t="n"/>
+      <c r="K46" s="15" t="n"/>
+      <c r="L46" s="15" t="n"/>
+      <c r="M46" s="15" t="n"/>
+      <c r="N46" s="15" t="n"/>
       <c r="O46" s="15" t="n"/>
-      <c r="P46" s="15" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="Q46" s="15" t="n">
-        <v>0.37</v>
-      </c>
+      <c r="P46" s="15" t="n"/>
+      <c r="Q46" s="15" t="n"/>
       <c r="R46" s="15" t="n"/>
-      <c r="S46" s="15" t="n">
-        <v>0.07000000000000001</v>
-      </c>
+      <c r="S46" s="15" t="n"/>
       <c r="T46" s="15" t="n"/>
       <c r="U46" s="15" t="n"/>
       <c r="V46" s="283">
@@ -38153,51 +38127,51 @@
         </is>
       </c>
       <c r="B26" s="104">
-        <f>10336.77+582693.24</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="C26" s="104">
-        <f>7918.25+674472.46</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="D26" s="104">
-        <f>15042.57+599506.15</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="E26" s="104">
-        <f>8599.51+630577.27</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="F26" s="104">
-        <f>13686.08+715022.85</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="G26" s="104">
-        <f>16443.85+600551.95</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="H26" s="104">
-        <f>16610.18+1048211.55</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="I26" s="104">
-        <f>10504+1103663.78</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="J26" s="104">
-        <f>6605.14+709321.76</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="K26" s="104">
-        <f>7623.58+1350327.62</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="L26" s="104">
-        <f>16123.15+1394695.61</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="M26" s="104">
-        <f>28059.59+797468.62</f>
+        <f>0+0</f>
         <v/>
       </c>
       <c r="N26" s="106">
@@ -38809,51 +38783,51 @@
         </is>
       </c>
       <c r="B39" s="104">
-        <f>639764.17-31179.33</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="C39" s="104">
-        <f>908618.94-32115.99</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="D39" s="104">
-        <f>670903.65-32015.54</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="E39" s="104">
-        <f>694562.86-30635.68</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="F39" s="104">
-        <f>815645.39-33028.7</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="G39" s="104">
-        <f>721284.95-34666.38</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="H39" s="104">
-        <f>1104755.48-34400.64</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="I39" s="104">
-        <f>1185146.89-35382.58</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="J39" s="104">
-        <f>806500.26-36920.05</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="K39" s="104">
-        <f>1595420.75-35703.68</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="L39" s="104">
-        <f>2076497.87-29878.4</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="M39" s="104">
-        <f>915058.23-40363.01</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="N39" s="90">
@@ -39063,7 +39037,7 @@
       <c r="K45" s="107" t="n"/>
       <c r="L45" s="107" t="n"/>
       <c r="M45" s="107">
-        <f>1194.83-710.83</f>
+        <f>0-0</f>
         <v/>
       </c>
       <c r="N45" s="90">

--- a/backend/app/aud/obligaciones_fiscales/templates/dm_obligaciones_fiscales.xlsx
+++ b/backend/app/aud/obligaciones_fiscales/templates/dm_obligaciones_fiscales.xlsx
@@ -2741,608 +2741,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>104775</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1483179</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="104775"/>
-          <a:ext cx="2245179" cy="704850"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>904874</colOff>
-      <row>1</row>
-      <rowOff>345281</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Imagen 9"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2028824" cy="792956"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1162050</colOff>
-      <row>1</row>
-      <rowOff>266700</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2390775" cy="685800"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>95250</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1721304</colOff>
-      <row>3</row>
-      <rowOff>28575</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="95250"/>
-          <a:ext cx="2245179" cy="781050"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>59531</colOff>
-      <row>0</row>
-      <rowOff>83344</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>690562</colOff>
-      <row>1</row>
-      <rowOff>229715</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagen 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="59531" y="83344"/>
-          <a:ext cx="2035969" cy="646434"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1290205</colOff>
-      <row>2</row>
-      <rowOff>294409</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2467841" cy="848591"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>666750</colOff>
-      <row>2</row>
-      <rowOff>333375</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagen 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2369344" cy="964406"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>1809750</colOff>
-      <row>2</row>
-      <rowOff>306915</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="2624667" cy="899582"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>16</col>
-      <colOff>517071</colOff>
-      <row>28</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>26</col>
-      <colOff>611333</colOff>
-      <row>37</row>
-      <rowOff>111381</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Imagen 1"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="19485428" y="5021036"/>
-          <a:ext cx="7904762" cy="1580952"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>1</col>
-      <colOff>710045</colOff>
-      <row>3</row>
-      <rowOff>17318</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="1827068" cy="961159"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>1466851</colOff>
-      <row>3</row>
-      <rowOff>9525</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="1" y="0"/>
-          <a:ext cx="1466850" cy="752475"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>0</col>
-      <colOff>3337428</colOff>
-      <row>13</row>
-      <rowOff>11906</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Imagen 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <lum bright="70000" contrast="-70000"/>
-        </a:blip>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="0"/>
-          <a:ext cx="3337428" cy="1059656"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -4220,7 +3618,6 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="60"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4748,8 +4145,6 @@
       </c>
       <c r="G28" s="332" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="326" t="inlineStr">
         <is>
@@ -6886,7 +6281,6 @@
     <mergeCell ref="B52:D52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7079,7 +6473,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="64"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7948,7 +7341,6 @@
     <brk id="8" min="0" max="1048575" man="1"/>
     <brk id="45" min="3" max="53" man="1"/>
   </colBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8978,7 +8370,6 @@
       <c r="D9" s="162" t="n"/>
       <c r="E9" s="196" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="207" t="n"/>
       <c r="B11" s="208" t="n"/>
@@ -10058,7 +9449,6 @@
       <c r="L41" s="79" t="n"/>
       <c r="M41" s="80" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="8" t="n"/>
     </row>
@@ -10096,7 +9486,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="36"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10508,8 +9897,6 @@
       <c r="E41" s="217" t="n"/>
     </row>
     <row r="42" ht="13.5" customHeight="1" thickTop="1"/>
-    <row r="43"/>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="170" t="inlineStr">
         <is>
@@ -10972,7 +10359,6 @@
       </c>
     </row>
     <row r="96" hidden="1" ht="13.5" customHeight="1" thickTop="1"/>
-    <row r="97"/>
     <row r="98">
       <c r="A98" s="8" t="n"/>
     </row>
@@ -11034,7 +10420,6 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="4" min="0" max="1048575" man="1"/>
   </colBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12094,7 +11479,6 @@
       <c r="L35" s="31" t="n"/>
       <c r="M35" s="31" t="n"/>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="539" t="inlineStr">
         <is>
@@ -13638,7 +13022,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="36"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -15120,7 +14503,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="B43" s="8" t="inlineStr">
         <is>
@@ -15210,7 +14592,6 @@
         <v/>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="463" t="inlineStr">
         <is>
@@ -15674,7 +15055,6 @@
         <v/>
       </c>
     </row>
-    <row r="57"/>
     <row r="58">
       <c r="C58" s="2" t="n"/>
     </row>
@@ -15784,7 +15164,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="25"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -33846,7 +33225,6 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="32" min="0" max="1048575" man="1"/>
   </colBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -34515,7 +33893,6 @@
       <c r="D10" s="541" t="n"/>
       <c r="E10" s="541" t="n"/>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -34542,7 +33919,6 @@
       <c r="C14" s="275" t="n"/>
       <c r="D14" s="275" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
@@ -37093,9 +36469,6 @@
       <c r="A71" s="194" t="n"/>
       <c r="B71" s="8" t="n"/>
     </row>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
     <row r="75">
       <c r="A75" s="131" t="inlineStr">
         <is>
@@ -37146,7 +36519,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="32"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -40426,7 +39798,6 @@
         </is>
       </c>
     </row>
-    <row r="75"/>
     <row r="76" hidden="1">
       <c r="A76" s="233" t="inlineStr">
         <is>
@@ -40764,7 +40135,6 @@
       <c r="C84" s="217" t="n"/>
       <c r="H84" s="217" t="n"/>
     </row>
-    <row r="85"/>
     <row r="86">
       <c r="B86" s="32" t="inlineStr">
         <is>
@@ -41072,10 +40442,6 @@
         </is>
       </c>
     </row>
-    <row r="104"/>
-    <row r="105"/>
-    <row r="106"/>
-    <row r="107"/>
     <row r="108">
       <c r="B108" s="3" t="inlineStr">
         <is>
@@ -41155,6 +40521,5 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="15" min="0" max="1048575" man="1"/>
   </colBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>